--- a/data/Bronze/informe_resultados_exito.xlsx
+++ b/data/Bronze/informe_resultados_exito.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\GitHub\Sistema-de-Pronostico-Financiero-Grupo-Exito\data\Bronze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DEB576E-619D-4A51-AF85-26CBFD5381C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8C0DFB-0D9B-449B-ABDF-481BA7A29278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10800" xr2:uid="{4FAB6009-2E41-4ADB-9B7C-9F679462B3CB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{4FAB6009-2E41-4ADB-9B7C-9F679462B3CB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>año</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>ebitda_recurrente</t>
-  </si>
-  <si>
-    <t>31/02/2019</t>
   </si>
 </sst>
 </file>
@@ -500,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2AD1993-4622-48ED-8616-A189F620CA32}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.85546875" bestFit="1" customWidth="1"/>
@@ -696,7 +693,7 @@
         <v>1286381</v>
       </c>
       <c r="F8" s="8">
-        <v>309922</v>
+        <v>342181</v>
       </c>
       <c r="G8" s="8">
         <v>-34733</v>
@@ -1111,479 +1108,8 @@
       </c>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
-        <v>2019</v>
-      </c>
-      <c r="B26" s="3">
-        <v>1</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="6">
-        <v>14275209</v>
-      </c>
-      <c r="E26" s="8">
-        <v>3307253</v>
-      </c>
-      <c r="F26" s="8">
-        <v>1010225</v>
-      </c>
-      <c r="G26" s="8">
-        <v>-13574</v>
-      </c>
-      <c r="H26" s="1"/>
-    </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
-        <v>2019</v>
-      </c>
-      <c r="B27" s="3">
-        <v>2</v>
-      </c>
-      <c r="C27" s="4">
-        <v>43646</v>
-      </c>
-      <c r="D27" s="6">
-        <v>14464569</v>
-      </c>
-      <c r="E27" s="8">
-        <v>3203710</v>
-      </c>
-      <c r="F27" s="8">
-        <v>968803</v>
-      </c>
-      <c r="G27" s="8">
-        <v>-18211</v>
-      </c>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
-        <v>2019</v>
-      </c>
-      <c r="B28" s="3">
-        <v>3</v>
-      </c>
-      <c r="C28" s="4">
-        <v>43738</v>
-      </c>
-      <c r="D28" s="6">
-        <v>3624469</v>
-      </c>
-      <c r="E28" s="8">
-        <v>917706</v>
-      </c>
-      <c r="F28" s="8">
-        <v>275353</v>
-      </c>
-      <c r="G28" s="8">
-        <v>11033</v>
-      </c>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="3">
-        <v>2019</v>
-      </c>
-      <c r="B29" s="3">
-        <v>4</v>
-      </c>
-      <c r="C29" s="4">
-        <v>43830</v>
-      </c>
-      <c r="D29" s="6">
-        <v>4324528</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1184311</v>
-      </c>
-      <c r="F29" s="8">
-        <v>470421</v>
-      </c>
-      <c r="G29" s="8">
-        <v>77121</v>
-      </c>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
-        <v>2018</v>
-      </c>
-      <c r="B30" s="3">
-        <v>1</v>
-      </c>
-      <c r="C30" s="4">
-        <v>43190</v>
-      </c>
-      <c r="D30" s="6">
-        <v>13743788</v>
-      </c>
-      <c r="E30" s="8">
-        <v>3261223</v>
-      </c>
-      <c r="F30" s="8">
-        <v>693605</v>
-      </c>
-      <c r="G30" s="8">
-        <v>9984</v>
-      </c>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
-        <v>2018</v>
-      </c>
-      <c r="B31" s="3">
-        <v>2</v>
-      </c>
-      <c r="C31" s="4">
-        <v>43281</v>
-      </c>
-      <c r="D31" s="6">
-        <v>12880590</v>
-      </c>
-      <c r="E31" s="8">
-        <v>3432313</v>
-      </c>
-      <c r="F31" s="8">
-        <v>1066086</v>
-      </c>
-      <c r="G31" s="8">
-        <v>119004</v>
-      </c>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
-        <v>2018</v>
-      </c>
-      <c r="B32" s="3">
-        <v>3</v>
-      </c>
-      <c r="C32" s="4">
-        <v>43373</v>
-      </c>
-      <c r="D32" s="6">
-        <v>12746030</v>
-      </c>
-      <c r="E32" s="8">
-        <v>2964673</v>
-      </c>
-      <c r="F32" s="8">
-        <v>661131</v>
-      </c>
-      <c r="G32" s="8">
-        <v>-9676</v>
-      </c>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
-        <v>2018</v>
-      </c>
-      <c r="B33" s="3">
-        <v>4</v>
-      </c>
-      <c r="C33" s="4">
-        <v>43465</v>
-      </c>
-      <c r="D33" s="6">
-        <v>15665762</v>
-      </c>
-      <c r="E33" s="8">
-        <v>3786351</v>
-      </c>
-      <c r="F33" s="8">
-        <v>1085498</v>
-      </c>
-      <c r="G33" s="8">
-        <v>160091</v>
-      </c>
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
-        <v>2017</v>
-      </c>
-      <c r="B34" s="3">
-        <v>1</v>
-      </c>
-      <c r="C34" s="4">
-        <v>42825</v>
-      </c>
-      <c r="D34" s="6">
-        <v>13525913</v>
-      </c>
-      <c r="E34" s="8">
-        <v>3237947</v>
-      </c>
-      <c r="F34" s="8">
-        <v>730915</v>
-      </c>
-      <c r="G34" s="8">
-        <v>-7593</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
-        <v>2017</v>
-      </c>
-      <c r="B35" s="3">
-        <v>2</v>
-      </c>
-      <c r="C35" s="4">
-        <v>42916</v>
-      </c>
-      <c r="D35" s="6">
-        <v>13267721</v>
-      </c>
-      <c r="E35" s="8">
-        <v>3569347</v>
-      </c>
-      <c r="F35" s="8">
-        <v>1058910</v>
-      </c>
-      <c r="G35" s="8">
-        <v>69263</v>
-      </c>
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
-        <v>2017</v>
-      </c>
-      <c r="B36" s="3">
-        <v>3</v>
-      </c>
-      <c r="C36" s="4">
-        <v>43008</v>
-      </c>
-      <c r="D36" s="6">
-        <v>13919543</v>
-      </c>
-      <c r="E36" s="8">
-        <v>3193655</v>
-      </c>
-      <c r="F36" s="8">
-        <v>670127</v>
-      </c>
-      <c r="G36" s="8">
-        <v>-31331</v>
-      </c>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
-        <v>2017</v>
-      </c>
-      <c r="B37" s="3">
-        <v>4</v>
-      </c>
-      <c r="C37" s="4">
-        <v>43100</v>
-      </c>
-      <c r="D37" s="6">
-        <v>15729626</v>
-      </c>
-      <c r="E37" s="8">
-        <v>4029674</v>
-      </c>
-      <c r="F37" s="8">
-        <v>1214818</v>
-      </c>
-      <c r="G37" s="8">
-        <v>187374</v>
-      </c>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
-        <v>2016</v>
-      </c>
-      <c r="B38" s="3">
-        <v>1</v>
-      </c>
-      <c r="C38" s="4">
-        <v>42460</v>
-      </c>
-      <c r="D38" s="6">
-        <v>18534935</v>
-      </c>
-      <c r="E38" s="8">
-        <v>4236720</v>
-      </c>
-      <c r="F38" s="8">
-        <v>599956</v>
-      </c>
-      <c r="G38" s="8">
-        <v>-104751</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="3">
-        <v>2016</v>
-      </c>
-      <c r="B39" s="3">
-        <v>2</v>
-      </c>
-      <c r="C39" s="4">
-        <v>42551</v>
-      </c>
-      <c r="D39" s="6">
-        <v>17805251</v>
-      </c>
-      <c r="E39" s="8">
-        <v>4608931</v>
-      </c>
-      <c r="F39" s="8">
-        <v>857146</v>
-      </c>
-      <c r="G39" s="8">
-        <v>-419906</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
-        <v>2016</v>
-      </c>
-      <c r="B40" s="3">
-        <v>3</v>
-      </c>
-      <c r="C40" s="4">
-        <v>42643</v>
-      </c>
-      <c r="D40" s="6">
-        <v>17405905</v>
-      </c>
-      <c r="E40" s="8">
-        <v>4436901</v>
-      </c>
-      <c r="F40" s="8">
-        <v>732685</v>
-      </c>
-      <c r="G40" s="8">
-        <v>-100304</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="3">
-        <v>2016</v>
-      </c>
-      <c r="B41" s="3">
-        <v>4</v>
-      </c>
-      <c r="C41" s="4">
-        <v>42735</v>
-      </c>
-      <c r="D41" s="6">
-        <v>14947487</v>
-      </c>
-      <c r="E41" s="8">
-        <v>3651466</v>
-      </c>
-      <c r="F41" s="8">
-        <v>1035185</v>
-      </c>
-      <c r="G41" s="8">
-        <v>191499</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
-        <v>2015</v>
-      </c>
-      <c r="B42" s="3">
-        <v>1</v>
-      </c>
-      <c r="C42" s="4">
-        <v>42094</v>
-      </c>
-      <c r="D42" s="6">
-        <v>3091400</v>
-      </c>
-      <c r="E42" s="8">
-        <v>781801</v>
-      </c>
-      <c r="F42" s="8">
-        <v>178858</v>
-      </c>
-      <c r="G42" s="8">
-        <v>69961</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
-        <v>2015</v>
-      </c>
-      <c r="B43" s="3">
-        <v>2</v>
-      </c>
-      <c r="C43" s="4">
-        <v>42185</v>
-      </c>
-      <c r="D43" s="6">
-        <v>2953483</v>
-      </c>
-      <c r="E43" s="8">
-        <v>762526</v>
-      </c>
-      <c r="F43" s="8">
-        <v>210373</v>
-      </c>
-      <c r="G43" s="8">
-        <v>170838</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
-        <v>2015</v>
-      </c>
-      <c r="B44" s="3">
-        <v>3</v>
-      </c>
-      <c r="C44" s="4">
-        <v>42277</v>
-      </c>
-      <c r="D44" s="6">
-        <v>7425520</v>
-      </c>
-      <c r="E44" s="8">
-        <v>1912745</v>
-      </c>
-      <c r="F44" s="8">
-        <v>478385</v>
-      </c>
-      <c r="G44" s="8">
-        <v>237262</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="3">
-        <v>2015</v>
-      </c>
-      <c r="B45" s="3">
-        <v>4</v>
-      </c>
-      <c r="C45" s="4">
-        <v>42369</v>
-      </c>
-      <c r="D45" s="6">
-        <v>19931808</v>
-      </c>
-      <c r="E45" s="8">
-        <v>4797297</v>
-      </c>
-      <c r="F45" s="8">
-        <v>1153708</v>
-      </c>
-      <c r="G45" s="8">
-        <v>195359</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C47" s="10"/>
+      <c r="C27" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
